--- a/textbook_examples/mod03_q06_power_query_answer.xlsx
+++ b/textbook_examples/mod03_q06_power_query_answer.xlsx
@@ -1571,45 +1571,45 @@
       <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="e">
-        <f>COUNTIF(#REF!,A6)</f>
-        <v>#REF!</v>
+      <c r="B6" s="8">
+        <f>COUNTIF(q06_tickets[crop],A6)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="e">
-        <f>COUNTIF(#REF!,A7)</f>
-        <v>#REF!</v>
+      <c r="B7" s="10">
+        <f>COUNTIF(q06_tickets[crop],A7)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="e">
-        <f>COUNTIF(#REF!,A8)</f>
-        <v>#REF!</v>
+      <c r="B8" s="10">
+        <f>COUNTIF(q06_tickets[crop],A8)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="e">
-        <f>COUNTIF(#REF!,A9)</f>
-        <v>#REF!</v>
+      <c r="B9" s="10">
+        <f>COUNTIF(q06_tickets[crop],A9)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="e">
-        <f>COUNTIF(#REF!,A10)</f>
-        <v>#REF!</v>
+      <c r="B10" s="12">
+        <f>COUNTIF(q06_tickets[crop],A10)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2">
